--- a/tracking_forms/012_service_advisor_follow_up_form--tracking_forms.xlsx
+++ b/tracking_forms/012_service_advisor_follow_up_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'first_name',_'value':_'first_name'}</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'First Name', 'value': 'first_name'}</t>
+          <t>first name</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'last_name',_'value':_'last_name'}</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Last Name', 'value': 'last_name'}</t>
+          <t>last name</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Email', 'value': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Phone', 'value': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'address_line_1',_'value':_'address_line_1'}</t>
+          <t>address_line_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Address Line 1', 'value': 'address_line_1'}</t>
+          <t>address line 1</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'address_line_2',_'value':_'address_line_2'}</t>
+          <t>address_line_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Address Line 2', 'value': 'address_line_2'}</t>
+          <t>address line 2</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'city',_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'City', 'value': 'city'}</t>
+          <t>city</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'state',_'value':_'state'}</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'State', 'value': 'state'}</t>
+          <t>state</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'zip',_'value':_'zip'}</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Zip', 'value': 'zip'}</t>
+          <t>zip</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'service_type',_'value':_'service_type'}</t>
+          <t>service_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Service Type', 'value': 'service_type'}</t>
+          <t>service type</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'service_date',_'value':_'service_date'}</t>
+          <t>service_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Service Date', 'value': 'service_date'}</t>
+          <t>service date</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'service_time',_'value':_'service_time'}</t>
+          <t>service_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Service Time', 'value': 'service_time'}</t>
+          <t>service time</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'service_advisor',_'value':_'service_advisor'}</t>
+          <t>service_advisor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Service Advisor', 'value': 'service_advisor'}</t>
+          <t>service advisor</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'vehicle_make',_'value':_'vehicle_make'}</t>
+          <t>vehicle_make</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Vehicle Make', 'value': 'vehicle_make'}</t>
+          <t>vehicle make</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'vehicle_model',_'value':_'vehicle_model'}</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Vehicle Model', 'value': 'vehicle_model'}</t>
+          <t>vehicle model</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'vehicle_year',_'value':_'vehicle_year'}</t>
+          <t>vehicle_year</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Vehicle Year', 'value': 'vehicle_year'}</t>
+          <t>vehicle year</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'very_likely',_'value':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Very Likely', 'value': 'very_likely'}</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'somewhat_likely',_'value':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Somewhat Likely', 'value': 'somewhat_likely'}</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'not_likely',_'value':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Not Likely', 'value': 'not_likely'}</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
